--- a/Configs/GameConfig/Datas/roguelike_weapon.xlsx
+++ b/Configs/GameConfig/Datas/roguelike_weapon.xlsx
@@ -260,7 +260,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -583,6 +583,41 @@
         <v>10.5</v>
       </c>
     </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>star_ring_pulse</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>星环脉冲</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>StarRingPulse</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>7</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J9" t="n">
+        <v>6.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
